--- a/backend/src/data/investigations.xlsx
+++ b/backend/src/data/investigations.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+  <si>
+    <t>ID</t>
+  </si>
   <si>
     <t>OP Number</t>
   </si>
@@ -31,25 +34,88 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Result</t>
+  </si>
+  <si>
     <t>Ordered Date</t>
   </si>
   <si>
-    <t>OP-2026-1001</t>
-  </si>
-  <si>
-    <t>Keerthika</t>
-  </si>
-  <si>
-    <t>Dr Kumar</t>
-  </si>
-  <si>
-    <t>MRI Scan</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>31/5/2026, 3:51:45 pm</t>
+    <t>52cb7c0c</t>
+  </si>
+  <si>
+    <t>OP-2024-001</t>
+  </si>
+  <si>
+    <t>Ravi Kumar Sharma</t>
+  </si>
+  <si>
+    <t>Dr. Meera Patel</t>
+  </si>
+  <si>
+    <t>X-Ray Knee AP/Lat</t>
+  </si>
+  <si>
+    <t>COMPLETED</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>2026-06-04T05:00:00.859Z</t>
+  </si>
+  <si>
+    <t>905e1ac7</t>
+  </si>
+  <si>
+    <t>Serum Uric Acid</t>
+  </si>
+  <si>
+    <t>7.2 mg/dL</t>
+  </si>
+  <si>
+    <t>2026-06-04T05:01:00.860Z</t>
+  </si>
+  <si>
+    <t>74864129</t>
+  </si>
+  <si>
+    <t>OP-2024-002</t>
+  </si>
+  <si>
+    <t>Lakshmi Devi Nellore</t>
+  </si>
+  <si>
+    <t>Dr. Ramesh Kumar</t>
+  </si>
+  <si>
+    <t>DEXA Bone Density Scan</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-06-04T05:45:00.860Z</t>
+  </si>
+  <si>
+    <t>4e66ec12</t>
+  </si>
+  <si>
+    <t>OP-2024-003</t>
+  </si>
+  <si>
+    <t>Suresh Babu Reddy</t>
+  </si>
+  <si>
+    <t>Dr. Anil Reddy</t>
+  </si>
+  <si>
+    <t>MRI Lumbar Spine</t>
+  </si>
+  <si>
+    <t>2026-06-04T06:30:00.860Z</t>
   </si>
 </sst>
 </file>
@@ -426,16 +492,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="4" width="25" customWidth="1"/>
-    <col min="5" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="5" width="25" customWidth="1"/>
+    <col min="6" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -457,28 +525,127 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>400</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="E2">
-        <v>2500</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D3" t="s">
         <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>200</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>1500</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5">
+        <v>4000</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
